--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_209_R21.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_209_R21.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.6742</v>
+        <v>11.2354</v>
       </c>
       <c r="E2" t="n">
-        <v>9.5908</v>
+        <v>8.883100000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0835</v>
+        <v>2.3523</v>
       </c>
       <c r="G2" t="n">
         <v>5.3575</v>
@@ -610,13 +610,13 @@
         <v>3.2473</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4611</v>
+        <v>1.0222</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9164</v>
+        <v>0.2087</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5447</v>
+        <v>0.8136</v>
       </c>
       <c r="V2" t="n">
         <v>1.6083</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>8.989100000000001</v>
+        <v>7.1772</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3132</v>
+        <v>4.7365</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6759</v>
+        <v>2.4407</v>
       </c>
       <c r="G3" t="n">
         <v>2.1248</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>4.042</v>
+        <v>2.2301</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8704</v>
+        <v>1.2937</v>
       </c>
       <c r="U3" t="n">
-        <v>1.1716</v>
+        <v>0.9364</v>
       </c>
       <c r="V3" t="n">
         <v>2.8223</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>K. PAPANIKOLAOU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3455</v>
+        <v>1.5862</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2659</v>
+        <v>-0.1772</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0796</v>
+        <v>1.7635</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.851</v>
+        <v>1.515</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6428</v>
+        <v>-1.4222</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5455</v>
+        <v>0.6757</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3983</v>
+        <v>2.2519</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1472</v>
+        <v>-1.5762</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3373</v>
+        <v>-0.5829</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5473</v>
+        <v>-0.7369</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.79</v>
+        <v>0.154</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.5515</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>1.9233</v>
+        <v>1.1018</v>
       </c>
       <c r="T4" t="n">
-        <v>1.0578</v>
+        <v>0.3068</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>1.214</v>
+        <v>-0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. PAPANIKOLAOU</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9629</v>
+        <v>1.1673</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.767</v>
+        <v>0.5582</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7299</v>
+        <v>0.6091</v>
       </c>
       <c r="G5" t="n">
-        <v>0.09279999999999999</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>1.515</v>
+        <v>0.851</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.4222</v>
+        <v>-1.6428</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6757</v>
+        <v>1.5455</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2519</v>
+        <v>1.3983</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.5762</v>
+        <v>0.1472</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5829</v>
+        <v>-2.3373</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7369</v>
+        <v>-0.5473</v>
       </c>
       <c r="O5" t="n">
-        <v>0.154</v>
+        <v>-1.79</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4784</v>
+        <v>0.7451</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2829</v>
+        <v>0.3501</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7613</v>
+        <v>0.3949</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5361</v>
+        <v>1.214</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2399</v>
+        <v>0.6382</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3207</v>
+        <v>-1.4332</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5606</v>
+        <v>2.0714</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0265</v>
+        <v>-2.0077</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2039</v>
+        <v>0.6256</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1774</v>
+        <v>-2.6333</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5418</v>
+        <v>0.9016999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5615</v>
+        <v>1.899</v>
       </c>
       <c r="L6" t="n">
-        <v>0.9802999999999999</v>
+        <v>-0.9973</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5153</v>
+        <v>-2.9094</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3577</v>
+        <v>-1.2734</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.1577</v>
+        <v>-1.636</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>-2.5515</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8556</v>
+        <v>4.4071</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4261</v>
+        <v>0.7903</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5975</v>
+        <v>0.2166</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1713</v>
+        <v>0.5737</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6072</v>
+        <v>-0.0712</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1409</v>
+        <v>0.5566</v>
       </c>
       <c r="F7" t="n">
-        <v>1.5337</v>
+        <v>-0.6278</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0077</v>
+        <v>0.0265</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6256</v>
+        <v>0.2039</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.6333</v>
+        <v>-0.1774</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9016999999999999</v>
+        <v>1.5418</v>
       </c>
       <c r="K7" t="n">
-        <v>1.899</v>
+        <v>0.5615</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.9973</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9094</v>
+        <v>-1.5153</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2734</v>
+        <v>-0.3577</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.636</v>
+        <v>-1.1577</v>
       </c>
       <c r="P7" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.8556</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-2.5515</v>
-      </c>
-      <c r="R7" t="n">
-        <v>4.4071</v>
-      </c>
       <c r="S7" t="n">
-        <v>-0.4551</v>
+        <v>-0.2574</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4911</v>
+        <v>-0.3615</v>
       </c>
       <c r="U7" t="n">
-        <v>0.036</v>
+        <v>0.1041</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4067</v>
+        <v>-0.7251</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7739</v>
+        <v>-1.9915</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3672</v>
+        <v>1.2664</v>
       </c>
       <c r="G8" t="n">
         <v>-1.5605</v>
@@ -1078,13 +1078,13 @@
         <v>3.0154</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7622</v>
+        <v>1.4438</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3418</v>
+        <v>0.4406</v>
       </c>
       <c r="U8" t="n">
-        <v>1.104</v>
+        <v>1.0031</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6332</v>
+        <v>-1.407</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.737</v>
+        <v>-1.5444</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1038</v>
+        <v>0.1374</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2669</v>
@@ -1156,13 +1156,13 @@
         <v>1.6237</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5768</v>
+        <v>0.803</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6528</v>
+        <v>0.8454</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V9" t="n">
         <v>2.1444</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1841</v>
+        <v>-1.5533</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8409</v>
+        <v>-2.1765</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6569</v>
+        <v>0.6232</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6797</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0523</v>
+        <v>0.6831</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1415</v>
+        <v>0.523</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1937</v>
+        <v>0.1601</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2525</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6014</v>
+        <v>-2.3752</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7895</v>
+        <v>-0.5969</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8119</v>
+        <v>-1.7783</v>
       </c>
       <c r="G11" t="n">
         <v>-3.2787</v>
@@ -1312,13 +1312,13 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1955</v>
+        <v>0.4217</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2715</v>
+        <v>0.4641</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6778999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.2992</v>
+        <v>15.6725</v>
       </c>
       <c r="E12" t="n">
-        <v>6.4414</v>
+        <v>6.814700000000003</v>
       </c>
       <c r="F12" t="n">
-        <v>8.858000000000001</v>
+        <v>8.857900000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-4.9837</v>
@@ -1390,10 +1390,10 @@
         <v>24.355</v>
       </c>
       <c r="S12" t="n">
-        <v>8.610400000000002</v>
+        <v>8.983699999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9141</v>
+        <v>4.2875</v>
       </c>
       <c r="U12" t="n">
         <v>4.696000000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8438</v>
+        <v>0.9738</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9745</v>
+        <v>1.0925</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1307</v>
+        <v>-0.1187</v>
       </c>
       <c r="G13" t="n">
         <v>0.9974</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0092</v>
+        <v>0.1208</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2161</v>
+        <v>-0.0982</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2069</v>
+        <v>0.219</v>
       </c>
       <c r="V13" t="n">
         <v>-1.0722</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. MIKE</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3078</v>
+        <v>0.2746</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8619</v>
+        <v>0.3447</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5541</v>
+        <v>-0.0701</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3076</v>
+        <v>0.4583</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.4332</v>
+        <v>0.2809</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7408</v>
+        <v>0.1774</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2062</v>
+        <v>0.3761</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1414</v>
+        <v>0.3025</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0647</v>
+        <v>0.0736</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8986</v>
+        <v>0.0822</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.5746</v>
+        <v>-0.0216</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6761</v>
+        <v>0.1038</v>
       </c>
       <c r="P14" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6387</v>
+        <v>0.1926</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3443</v>
+        <v>-0.0314</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7055</v>
+        <v>0.224</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>I. MIKE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0222</v>
+        <v>0.1189</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2267</v>
+        <v>2.0978</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2045</v>
+        <v>-1.9789</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4583</v>
+        <v>1.3076</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2809</v>
+        <v>-2.4332</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1774</v>
+        <v>3.7408</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3761</v>
+        <v>3.2062</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3025</v>
+        <v>0.1414</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0736</v>
+        <v>3.0647</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0822</v>
+        <v>-1.8986</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0216</v>
+        <v>-2.5746</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1038</v>
+        <v>0.6761</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0597</v>
+        <v>-0.8276</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1494</v>
+        <v>-1.1084</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0896</v>
+        <v>0.2807</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5053</v>
+        <v>-0.3373</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.1788</v>
+        <v>-0.497</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6735</v>
+        <v>0.1598</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3798</v>
+        <v>1.5423</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7851</v>
+        <v>-0.0336</v>
       </c>
       <c r="I16" t="n">
-        <v>2.1648</v>
+        <v>1.576</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7303</v>
+        <v>2.2322</v>
       </c>
       <c r="K16" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.8605</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6428</v>
+        <v>1.3717</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3505</v>
+        <v>-0.6899</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.8726</v>
+        <v>-0.8942</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5221</v>
+        <v>0.2042</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8556</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q16" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0294</v>
+        <v>-0.7431</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5702</v>
+        <v>-0.3222</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5996</v>
+        <v>-0.4208</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.1829</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>0.1107</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0386</v>
+        <v>-0.8091</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.615</v>
+        <v>-1.6506</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4236</v>
+        <v>0.8415</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5423</v>
+        <v>1.3798</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0336</v>
+        <v>-0.7851</v>
       </c>
       <c r="I17" t="n">
-        <v>1.576</v>
+        <v>2.1648</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2322</v>
+        <v>1.7303</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8605</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3717</v>
+        <v>1.6428</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6899</v>
+        <v>-0.3505</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8942</v>
+        <v>-0.8726</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2042</v>
+        <v>0.5221</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.3195</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q17" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4444</v>
+        <v>-0.3332</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4402</v>
+        <v>0.0984</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.0042</v>
+        <v>-0.4316</v>
       </c>
       <c r="V17" t="n">
-        <v>1.1829</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>N. DIMITRIJEVIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3163</v>
+        <v>-1.9598</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5303</v>
+        <v>-1.1362</v>
       </c>
       <c r="F18" t="n">
-        <v>0.214</v>
+        <v>-0.8236</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3307</v>
+        <v>1.8441</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1982</v>
+        <v>-0.0564</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5288</v>
+        <v>1.9005</v>
       </c>
       <c r="J18" t="n">
-        <v>2.4293</v>
+        <v>3.31</v>
       </c>
       <c r="K18" t="n">
-        <v>2.2084</v>
+        <v>1.6672</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2208</v>
+        <v>1.6428</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.0986</v>
+        <v>-1.4659</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.4066</v>
+        <v>-1.7236</v>
       </c>
       <c r="O18" t="n">
-        <v>0.308</v>
+        <v>0.2578</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.0154</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.7988</v>
+        <v>-3.7112</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7834</v>
+        <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>0.9045</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3031</v>
+        <v>-0.735</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6014</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
       <c r="W18" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>N. DIMITRIJEVIC</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.8463</v>
+        <v>-1.9754</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3721</v>
+        <v>-0.7195</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4742</v>
+        <v>-1.256</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8441</v>
+        <v>-0.2408</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0564</v>
+        <v>-0.5653</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9005</v>
+        <v>0.3246</v>
       </c>
       <c r="J19" t="n">
-        <v>3.31</v>
+        <v>1.2499</v>
       </c>
       <c r="K19" t="n">
-        <v>1.6672</v>
+        <v>1.1798</v>
       </c>
       <c r="L19" t="n">
-        <v>1.6428</v>
+        <v>0.0701</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4659</v>
+        <v>-1.4907</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7236</v>
+        <v>-1.7452</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2578</v>
+        <v>0.2545</v>
       </c>
       <c r="P19" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-1.3917</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-3.7112</v>
-      </c>
       <c r="R19" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.6904</v>
+        <v>-1.1264</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9709</v>
+        <v>-0.5777</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7196</v>
+        <v>-0.5487</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.042</v>
+        <v>-2.0969</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9554</v>
+        <v>-2.3098</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0867</v>
+        <v>0.2129</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2408</v>
+        <v>-2.5476</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5653</v>
+        <v>-2.2664</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3246</v>
+        <v>-0.2811</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2499</v>
+        <v>-0.1631</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1798</v>
+        <v>0.1617</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0701</v>
+        <v>-0.3248</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.4907</v>
+        <v>-2.3844</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7452</v>
+        <v>-2.4282</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2545</v>
+        <v>0.0437</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>2.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.193</v>
+        <v>-1.4438</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8136</v>
+        <v>-1.2577</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3794</v>
+        <v>-0.186</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>2.8223</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2586</v>
+        <v>-3.1013</v>
       </c>
       <c r="E21" t="n">
         <v>-2.7239</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5347</v>
+        <v>-0.3775</v>
       </c>
       <c r="G21" t="n">
         <v>-0.0881</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.637</v>
+        <v>-0.4797</v>
       </c>
       <c r="T21" t="n">
         <v>-0.1415</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4955</v>
+        <v>-0.3383</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6778999999999999</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4659</v>
+        <v>-3.2414</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5457</v>
+        <v>-3.356</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9203</v>
+        <v>0.1145</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5476</v>
+        <v>0.3307</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.2664</v>
+        <v>-0.1982</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2811</v>
+        <v>0.5288</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1631</v>
+        <v>2.4293</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1617</v>
+        <v>2.2084</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.3248</v>
+        <v>0.2208</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.3844</v>
+        <v>-2.0986</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.4282</v>
+        <v>-2.4066</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0437</v>
+        <v>0.308</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9278</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.7112</v>
+        <v>-5.7988</v>
       </c>
       <c r="R22" t="n">
         <v>2.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.8128</v>
+        <v>-0.0206</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4936</v>
+        <v>-0.5226</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.3192</v>
+        <v>0.5019</v>
       </c>
       <c r="V22" t="n">
-        <v>2.8223</v>
+        <v>-0.5361</v>
       </c>
       <c r="W22" t="n">
-        <v>2.8223</v>
+        <v>0.5361</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-15.2992</v>
+        <v>-12.1539</v>
       </c>
       <c r="E23" t="n">
-        <v>-8.8581</v>
+        <v>-8.858000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.4413</v>
+        <v>-3.2961</v>
       </c>
       <c r="G23" t="n">
-        <v>4.983700000000001</v>
+        <v>4.9837</v>
       </c>
       <c r="H23" t="n">
         <v>-5.7738</v>
@@ -2239,7 +2239,7 @@
         <v>2.3102</v>
       </c>
       <c r="P23" t="n">
-        <v>-6.958500000000001</v>
+        <v>-6.9585</v>
       </c>
       <c r="Q23" t="n">
         <v>-24.355</v>
@@ -2248,22 +2248,22 @@
         <v>17.3965</v>
       </c>
       <c r="S23" t="n">
-        <v>-8.610099999999999</v>
+        <v>-5.4649</v>
       </c>
       <c r="T23" t="n">
-        <v>-4.6963</v>
+        <v>-4.696299999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.9141</v>
+        <v>-0.7687999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-4.7142</v>
+        <v>-4.714200000000001</v>
       </c>
       <c r="W23" t="n">
         <v>4.4306</v>
       </c>
       <c r="X23" t="n">
-        <v>-9.144799999999998</v>
+        <v>-9.1448</v>
       </c>
     </row>
   </sheetData>
